--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -1,77 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pks_aito/Documents/GitHub/dl-project/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D335518-A7C6-1648-AD09-659EAF4399A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="20" yWindow="680" windowWidth="29400" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Experiments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Experiments" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Model Name</t>
+  </si>
+  <si>
+    <t>Hyperparameters</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Overfit (O) / Underfit (U) / Just Right (B)</t>
+  </si>
+  <si>
+    <t>batch_size</t>
+  </si>
+  <si>
+    <t>epochs</t>
+  </si>
+  <si>
+    <t>learning_rate</t>
+  </si>
+  <si>
+    <t>Train Accuracy</t>
+  </si>
+  <si>
+    <t>Test Accuracy</t>
+  </si>
+  <si>
+    <t>ModelBaseline</t>
+  </si>
+  <si>
+    <t>1.00e-03</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>ModelImproved</t>
+  </si>
+  <si>
+    <t>3.00e-04</t>
+  </si>
+  <si>
+    <t>ModelFinal</t>
+  </si>
+  <si>
+    <t>1.00e-04</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00843C0C"/>
+        <fgColor rgb="FF843C0C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00375623"/>
+        <fgColor rgb="FF375623"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -81,48 +147,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </left>
       <right style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </right>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </left>
       <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </bottom>
       <diagonal/>
     </border>
@@ -130,43 +177,23 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </right>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </bottom>
       <diagonal/>
     </border>
@@ -174,102 +201,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -557,178 +531,214 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Model Name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Hyperparameters</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Overfit (O) / Underfit (U) / Just Right (B)</t>
-        </is>
+    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="8"/>
+      <c r="H1" s="11" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>batch_size</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>epochs</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>learning_rate</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Train Accuracy</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Test Accuracy</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="n"/>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="10"/>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>ModelBaseline</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
         <v>32</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>1.00e-03</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3">
         <v>68.2</v>
       </c>
-      <c r="G3" s="7" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+      <c r="G3" s="3">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>ModelImproved</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5">
         <v>32</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="5">
         <v>2</v>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>3.00e-04</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+      <c r="E4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="G4" s="5">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>ModelFinal</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3">
+        <v>80.8</v>
+      </c>
+      <c r="G5" s="3">
+        <v>82.5</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5">
         <v>32</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>1.00e-04</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+      <c r="D6" s="5">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="5">
+        <v>85</v>
+      </c>
+      <c r="G6" s="5">
+        <v>84.1</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3">
+        <v>95.7</v>
+      </c>
+      <c r="G7" s="3">
+        <v>90.5</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5">
+        <v>32</v>
+      </c>
+      <c r="D8" s="5">
+        <v>29</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="5">
+        <v>97.4</v>
+      </c>
+      <c r="G8" s="5">
+        <v>89.7</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pks_aito/Documents/GitHub/dl-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D335518-A7C6-1648-AD09-659EAF4399A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BAB35B-4A79-744B-A5A7-D22E0944B963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="680" windowWidth="29400" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>No</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>1.00e-04</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
 </sst>
 </file>
@@ -608,7 +611,7 @@
         <v>78.099999999999994</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -634,7 +637,7 @@
         <v>78.900000000000006</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -674,7 +677,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="5">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>11</v>
@@ -726,7 +729,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>16</v>
